--- a/会议船舶顺序.xlsx
+++ b/会议船舶顺序.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16300" windowHeight="15700"/>
+    <workbookView windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -59,67 +59,67 @@
     <t>KATORIN 1</t>
   </si>
   <si>
+    <t>ZEVIROUS (Malaysia)</t>
+  </si>
+  <si>
+    <t>HARRIET 1</t>
+  </si>
+  <si>
+    <t>HEBE</t>
+  </si>
+  <si>
+    <t>HELOISE</t>
+  </si>
+  <si>
+    <t>HERA</t>
+  </si>
+  <si>
+    <t>FILENE</t>
+  </si>
+  <si>
+    <t>HANA</t>
+  </si>
+  <si>
+    <t>FUYU</t>
+  </si>
+  <si>
+    <t>WENSHENG</t>
+  </si>
+  <si>
+    <t>HAIDA</t>
+  </si>
+  <si>
+    <t>HAI YOU 168</t>
+  </si>
+  <si>
+    <t>INTAN</t>
+  </si>
+  <si>
+    <t>PP5711</t>
+  </si>
+  <si>
+    <t>PACIFIC FREEDOM</t>
+  </si>
+  <si>
+    <t>SILVER ELITE</t>
+  </si>
+  <si>
+    <t>ARCH</t>
+  </si>
+  <si>
+    <t>OCEAN REGENT</t>
+  </si>
+  <si>
+    <t>IBU</t>
+  </si>
+  <si>
+    <t>LUBS</t>
+  </si>
+  <si>
+    <t>ARTEMIS</t>
+  </si>
+  <si>
     <t>OCEAN FORTUNE 18</t>
-  </si>
-  <si>
-    <t>ZEVIROUS (Malaysia)</t>
-  </si>
-  <si>
-    <t>HARRIET 1</t>
-  </si>
-  <si>
-    <t>HEBE</t>
-  </si>
-  <si>
-    <t>HELOISE</t>
-  </si>
-  <si>
-    <t>HERA</t>
-  </si>
-  <si>
-    <t>FILENE</t>
-  </si>
-  <si>
-    <t>HANA</t>
-  </si>
-  <si>
-    <t>FUYU</t>
-  </si>
-  <si>
-    <t>WENSHENG</t>
-  </si>
-  <si>
-    <t>HAIDA</t>
-  </si>
-  <si>
-    <t>HAI YOU 168</t>
-  </si>
-  <si>
-    <t>INTAN</t>
-  </si>
-  <si>
-    <t>PP5711</t>
-  </si>
-  <si>
-    <t>PACIFIC FREEDOM</t>
-  </si>
-  <si>
-    <t>SILVER ELITE</t>
-  </si>
-  <si>
-    <t>ARCH</t>
-  </si>
-  <si>
-    <t>OCEAN REGENT</t>
-  </si>
-  <si>
-    <t>IBU</t>
-  </si>
-  <si>
-    <t>LUBS</t>
-  </si>
-  <si>
-    <t>ARTEMIS</t>
   </si>
   <si>
     <t>ARINE</t>
